--- a/data/trans_dic/ProbViv_estruc-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_estruc-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con problemas estructurales en la vivienda (goteras, humedades, podredumbre)</t>
+          <t>Hogares con problemas estructurales en la vivienda (goteras, humedades, podredumbre) (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,82; 20,19</t>
+          <t>13,74; 19,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,25; 17,83</t>
+          <t>13,16; 17,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,15; 17,82</t>
+          <t>14,16; 17,8</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,42; 9,31</t>
+          <t>5,47; 9,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,31; 40,63</t>
+          <t>8,38; 39,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,81; 27,88</t>
+          <t>7,83; 26,42</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,85; 9,46</t>
+          <t>4,94; 9,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,9; 8,4</t>
+          <t>4,85; 8,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,38; 8,29</t>
+          <t>5,38; 8,4</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,74; 10,16</t>
+          <t>6,68; 10,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,34; 29,94</t>
+          <t>9,39; 30,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,01; 21,58</t>
+          <t>9,02; 21,34</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con problemas estructurales en la vivienda (goteras, humedades, podredumbre)</t>
+          <t>Hogares con problemas estructurales en la vivienda (goteras, humedades, podredumbre) (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>71184; 103960</t>
+          <t>70736; 101496</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>100010; 134598</t>
+          <t>99350; 135275</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>179642; 226289</t>
+          <t>179829; 226011</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>124013; 213197</t>
+          <t>125129; 211809</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>185940; 909007</t>
+          <t>187417; 880411</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>353519; 1261966</t>
+          <t>354441; 1195711</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>31349; 61141</t>
+          <t>31952; 60637</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>32304; 55373</t>
+          <t>31954; 54823</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>70176; 108257</t>
+          <t>70265; 109726</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>232524; 350497</t>
+          <t>230551; 348631</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>340996; 1093049</t>
+          <t>342790; 1123336</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>639916; 1532409</t>
+          <t>640558; 1515188</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/ProbViv_estruc-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_estruc-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,74; 19,71</t>
+          <t>14,76; 20,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,16; 17,92</t>
+          <t>13,51; 17,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,16; 17,8</t>
+          <t>14,58; 18,0</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,47; 9,25</t>
+          <t>7,58; 10,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,38; 39,36</t>
+          <t>8,56; 11,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,83; 26,42</t>
+          <t>8,5; 10,45</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,94; 9,38</t>
+          <t>5,04; 9,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,85; 8,32</t>
+          <t>5,03; 8,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,38; 8,4</t>
+          <t>5,5; 8,14</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,68; 10,1</t>
+          <t>8,91; 11,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,39; 30,77</t>
+          <t>9,39; 11,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,02; 21,34</t>
+          <t>9,51; 10,93</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>85586</t>
+          <t>102092</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>115160</t>
+          <t>125693</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>200746</t>
+          <t>227786</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>70736; 101496</t>
+          <t>85379; 121437</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>99350; 135275</t>
+          <t>110971; 143660</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>179829; 226011</t>
+          <t>204052; 252042</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>175373</t>
+          <t>199679</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>383269</t>
+          <t>212168</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>558642</t>
+          <t>411847</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>125129; 211809</t>
+          <t>169022; 231470</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>187417; 880411</t>
+          <t>185737; 240142</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>354441; 1195711</t>
+          <t>374233; 460016</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>44814</t>
+          <t>50108</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42390</t>
+          <t>47664</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87204</t>
+          <t>97772</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>31952; 60637</t>
+          <t>35886; 66063</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>31954; 54823</t>
+          <t>36879; 61581</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>70265; 109726</t>
+          <t>79483; 117538</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>305774</t>
+          <t>351880</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>540819</t>
+          <t>385525</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>846593</t>
+          <t>737405</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>230551; 348631</t>
+          <t>313476; 390852</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>342790; 1123336</t>
+          <t>349909; 425236</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>640558; 1515188</t>
+          <t>689008; 791731</t>
         </is>
       </c>
     </row>
